--- a/output/2026-10-03_14_Malesia_Perlis_Componentistica_Ventilazione_industriale.xlsx
+++ b/output/2026-10-03_14_Malesia_Perlis_Componentistica_Ventilazione_industriale.xlsx
@@ -506,7 +506,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Reg. impresa 202001000892 (1357211-X). Produttore/rivenditore ventilatori solari/eolici da tetto 'German Sunpower' per uso industriale, commerciale, residenziale. Copertura dichiarata su Perlis (Kangar, Kuala Perlis, Padang Besar, Arau, Pauh) non direttamente riscontrata nel sito ufficiale. Fonte: sito ufficiale.</t>
+          <t>Reg. impresa 202001000892 (1357211-X). Produttore/rivenditore ventilatori solari/eolici da tetto 'German Sunpower' per uso industriale, commerciale, residenziale. Copertura dichiarata su Perlis (Kangar, Kuala Perlis, Padang Besar, Arau, Pauh) non direttamente riscontrata nel sito ufficiale. Fonte: sito ufficiale. [DUPLICATO — vedi anche: 2026-09-30_19_Malesia_Johor_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -541,10 +541,9 @@
           <t>+60 11-1016 1902</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Distributore multi-categoria di utensili/macchinari/MRO dal 1977, sezione dedicata 'Fans &amp; Ventilation' (exhaust fan, blower fan, air mover). Vendita online con consegna in Malesia peninsulare. Fonte: sito ufficiale.</t>
+          <t>Distributore multi-categoria di utensili/macchinari/MRO dal 1977, sezione dedicata 'Fans &amp; Ventilation' (exhaust fan, blower fan, air mover). Vendita online con consegna in Malesia peninsulare. Fonte: sito ufficiale. [DUPLICATO — vedi anche: 2026-10-02_19_Malesia_Negeri_Sembilan_Componentistica_Ventilazione_industriale.xlsx]</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -579,7 +578,6 @@
           <t>+603-7846 0340</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>Produzione/distribuzione ventilatori industriali e accessori. Certificazioni ISO 9001:2015 ed EN 12101-3:2015. Fonte: directory BSI Group + sito ufficiale.</t>
@@ -587,7 +585,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -617,7 +615,6 @@
           <t>+60-9-859 2095</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Azienda Bumiputera 100%, costituita 2015, vincitrice SME100 Award 2025. Soluzioni LEV, HVAC, APCS, igiene industriale. WhatsApp +60 12-742 0302. Fonte: sito ufficiale + sme100.asia.</t>
@@ -625,7 +622,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -655,7 +652,6 @@
           <t>+603-3324 3638</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>Filiale malese del gruppo olandese Vostermans Companies (dal 1952). Ventilatori assiali Multifan per uso agricolo/industriale. Referente GM: Mohamed Maqbool, +6012-683 8488. Fonte: mdbc.com.my, wattagnet.com.</t>
@@ -663,7 +659,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
@@ -673,7 +669,6 @@
           <t>Mewahtech Solution Sdn Bhd</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>Kuala Lumpur (W.P.) - copertura nazionale dichiarata, Perlis non confermata</t>
@@ -684,8 +679,6 @@
           <t>Componentistica / Ventilazione industriale</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>Trading/mechanical project supply, HVAC/plumbing incl. ventilazione, 20 anni di attività dichiarati. Esistenza confermata solo da directory locale (magicpin, rating 5.0); contatti non verificabili con fonte affidabile - approfondire prima di contatto commerciale.</t>
@@ -693,7 +686,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (05/10/2026)</t>
         </is>
       </c>
     </row>
